--- a/DATA/MODELADO/Diagnosticos/Exp01/recomendaciones_Exp01.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp01/recomendaciones_Exp01.xlsx
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>• Aplicar balanceo de clases (SMOTE, Oversampling o Undersampling).</t>
+          <t>• Aplicar técnicas de balanceo de clases (SMOTE, Oversampling o Undersampling).</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Ajustar el umbral de decisión diferente de 0.50.</t>
+          <t>• Ajustar el umbral de decisión a un valor diferente de 0.50.</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>• El conjunto presenta desbalance de clases; utilizar técnicas de balanceo antes del entrenamiento.</t>
+          <t>• El conjunto presenta desbalance de clases; aplicar técnicas de balanceo antes del entrenamiento.</t>
         </is>
       </c>
     </row>
